--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run2/epoch_90/per_file_predictions_epoch_90.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run2/epoch_90/per_file_predictions_epoch_90.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="521">
   <si>
     <t>Filename</t>
   </si>
@@ -808,772 +808,775 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0,1,0,1</t>
-  </si>
-  <si>
-    <t>0.3433,0.2138,0.0055,0.4976</t>
-  </si>
-  <si>
-    <t>0.0200,0.0008,0.0018,0.9904</t>
-  </si>
-  <si>
-    <t>0.6468,0.0142,0.0043,0.4073</t>
-  </si>
-  <si>
-    <t>0.0844,0.0188,0.0048,0.9629</t>
-  </si>
-  <si>
-    <t>0.9955,0.0028,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9974,0.0005,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.9927,0.0032,0.0012,0.0005</t>
-  </si>
-  <si>
-    <t>0.9888,0.0117,0.0016,0.0001</t>
-  </si>
-  <si>
-    <t>0.9859,0.0130,0.0020,0.0005</t>
-  </si>
-  <si>
-    <t>0.9939,0.0042,0.0005,0.0003</t>
-  </si>
-  <si>
-    <t>0.9962,0.0006,0.0001,0.0010</t>
-  </si>
-  <si>
-    <t>0.9984,0.0004,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.8434,0.0412,0.0664,0.0254</t>
-  </si>
-  <si>
-    <t>0.1865,0.2962,0.5931,0.0132</t>
-  </si>
-  <si>
-    <t>0.4595,0.0022,0.7764,0.0013</t>
-  </si>
-  <si>
-    <t>0.1003,0.0450,0.8589,0.0090</t>
-  </si>
-  <si>
-    <t>0.8073,0.0282,0.1918,0.0132</t>
-  </si>
-  <si>
-    <t>0.0055,0.9868,0.0099,0.0004</t>
-  </si>
-  <si>
-    <t>0.0015,0.9949,0.0078,0.0004</t>
-  </si>
-  <si>
-    <t>0.2214,0.7445,0.0673,0.0079</t>
-  </si>
-  <si>
-    <t>0.0545,0.9390,0.0111,0.0010</t>
-  </si>
-  <si>
-    <t>0.0045,0.9925,0.0046,0.0001</t>
-  </si>
-  <si>
-    <t>0.2154,0.0073,0.8349,0.0144</t>
-  </si>
-  <si>
-    <t>0.2180,0.0317,0.4473,0.3414</t>
-  </si>
-  <si>
-    <t>0.0148,0.0024,0.9870,0.0018</t>
-  </si>
-  <si>
-    <t>0.2555,0.0515,0.7108,0.0297</t>
-  </si>
-  <si>
-    <t>0.0247,0.0087,0.9716,0.0065</t>
-  </si>
-  <si>
-    <t>0.0721,0.0043,0.9477,0.0025</t>
-  </si>
-  <si>
-    <t>0.0030,0.0020,0.9849,0.0193</t>
-  </si>
-  <si>
-    <t>0.1514,0.8336,0.0400,0.0013</t>
-  </si>
-  <si>
-    <t>0.2840,0.6430,0.1228,0.0309</t>
-  </si>
-  <si>
-    <t>0.0030,0.0167,0.9916,0.0027</t>
-  </si>
-  <si>
-    <t>0.0084,0.9545,0.1239,0.0013</t>
-  </si>
-  <si>
-    <t>0.5740,0.4367,0.0214,0.0128</t>
-  </si>
-  <si>
-    <t>0.7487,0.2082,0.0645,0.0215</t>
-  </si>
-  <si>
-    <t>0.8160,0.2602,0.0068,0.0012</t>
-  </si>
-  <si>
-    <t>0.0237,0.9507,0.0807,0.0035</t>
-  </si>
-  <si>
-    <t>0.0213,0.8284,0.6297,0.0041</t>
-  </si>
-  <si>
-    <t>0.0239,0.0747,0.8994,0.0589</t>
-  </si>
-  <si>
-    <t>0.0082,0.8254,0.8167,0.0027</t>
-  </si>
-  <si>
-    <t>0.2540,0.0193,0.5557,0.1640</t>
-  </si>
-  <si>
-    <t>0.0619,0.0860,0.9204,0.0016</t>
-  </si>
-  <si>
-    <t>0.0010,0.9960,0.0027,0.0001</t>
-  </si>
-  <si>
-    <t>0.0166,0.0249,0.9667,0.0057</t>
-  </si>
-  <si>
-    <t>0.0463,0.7465,0.0091,0.8798</t>
-  </si>
-  <si>
-    <t>0.0037,0.9852,0.0175,0.0017</t>
-  </si>
-  <si>
-    <t>0.0018,0.9740,0.0182,0.0138</t>
-  </si>
-  <si>
-    <t>0.0025,0.9873,0.0150,0.0017</t>
-  </si>
-  <si>
-    <t>0.0090,0.2191,0.8844,0.0124</t>
-  </si>
-  <si>
-    <t>0.0058,0.2591,0.9725,0.0015</t>
-  </si>
-  <si>
-    <t>0.0170,0.0066,0.9848,0.0012</t>
-  </si>
-  <si>
-    <t>0.2441,0.0018,0.8997,0.0012</t>
-  </si>
-  <si>
-    <t>0.0064,0.0222,0.9829,0.0058</t>
-  </si>
-  <si>
-    <t>0.0691,0.0732,0.8951,0.0015</t>
-  </si>
-  <si>
-    <t>0.9359,0.0632,0.0082,0.0035</t>
-  </si>
-  <si>
-    <t>0.9856,0.0082,0.0030,0.0010</t>
-  </si>
-  <si>
-    <t>0.9350,0.0634,0.0115,0.0057</t>
-  </si>
-  <si>
-    <t>0.0219,0.0752,0.9713,0.0036</t>
-  </si>
-  <si>
-    <t>0.9721,0.0270,0.0049,0.0004</t>
-  </si>
-  <si>
-    <t>0.9728,0.0253,0.0045,0.0007</t>
-  </si>
-  <si>
-    <t>0.9169,0.1227,0.0011,0.0015</t>
-  </si>
-  <si>
-    <t>0.0009,0.8478,0.9679,0.0001</t>
-  </si>
-  <si>
-    <t>0.0274,0.0760,0.9454,0.0029</t>
-  </si>
-  <si>
-    <t>0.0373,0.4905,0.6970,0.0326</t>
-  </si>
-  <si>
-    <t>0.0033,0.8026,0.9235,0.0005</t>
-  </si>
-  <si>
-    <t>0.0326,0.0116,0.9697,0.0031</t>
-  </si>
-  <si>
-    <t>0.0197,0.8149,0.3311,0.0004</t>
-  </si>
-  <si>
-    <t>0.0115,0.9893,0.0009,0.0000</t>
-  </si>
-  <si>
-    <t>0.6629,0.0127,0.4609,0.0125</t>
-  </si>
-  <si>
-    <t>0.7040,0.2615,0.0358,0.0114</t>
-  </si>
-  <si>
-    <t>0.0135,0.0211,0.9764,0.0036</t>
-  </si>
-  <si>
-    <t>0.0013,0.9118,0.8474,0.0001</t>
-  </si>
-  <si>
-    <t>0.0285,0.4306,0.8218,0.0011</t>
-  </si>
-  <si>
-    <t>0.0017,0.9884,0.0723,0.0002</t>
-  </si>
-  <si>
-    <t>0.0012,0.9159,0.9156,0.0001</t>
-  </si>
-  <si>
-    <t>0.0206,0.0282,0.1151,0.9235</t>
-  </si>
-  <si>
-    <t>0.0015,0.0180,0.0002,0.9986</t>
-  </si>
-  <si>
-    <t>0.0049,0.0019,0.0010,0.9963</t>
-  </si>
-  <si>
-    <t>0.0192,0.0018,0.0020,0.9898</t>
-  </si>
-  <si>
-    <t>0.0388,0.0199,0.0210,0.9655</t>
-  </si>
-  <si>
-    <t>0.0087,0.0023,0.0101,0.9873</t>
-  </si>
-  <si>
-    <t>0.0006,0.9648,0.7884,0.0002</t>
-  </si>
-  <si>
-    <t>0.0018,0.8818,0.9377,0.0001</t>
-  </si>
-  <si>
-    <t>0.0054,0.8628,0.7742,0.0008</t>
-  </si>
-  <si>
-    <t>0.0066,0.8057,0.7544,0.0018</t>
-  </si>
-  <si>
-    <t>0.0059,0.8776,0.7539,0.0006</t>
-  </si>
-  <si>
-    <t>0.0086,0.8229,0.8202,0.0017</t>
-  </si>
-  <si>
-    <t>0.9941,0.0023,0.0005,0.0004</t>
-  </si>
-  <si>
-    <t>0.9552,0.0609,0.0031,0.0006</t>
-  </si>
-  <si>
-    <t>0.9796,0.0276,0.0011,0.0004</t>
-  </si>
-  <si>
-    <t>0.9853,0.0101,0.0016,0.0007</t>
-  </si>
-  <si>
-    <t>0.9894,0.0030,0.0010,0.0016</t>
-  </si>
-  <si>
-    <t>0.9945,0.0032,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9305,0.0846,0.0048,0.0007</t>
-  </si>
-  <si>
-    <t>0.9853,0.0110,0.0015,0.0009</t>
-  </si>
-  <si>
-    <t>0.9971,0.0008,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9951,0.0027,0.0010,0.0002</t>
-  </si>
-  <si>
-    <t>0.9948,0.0010,0.0003,0.0012</t>
-  </si>
-  <si>
-    <t>0.9982,0.0003,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9929,0.0021,0.0002,0.0011</t>
-  </si>
-  <si>
-    <t>0.9956,0.0023,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.9952,0.0010,0.0001,0.0011</t>
-  </si>
-  <si>
-    <t>0.9905,0.0083,0.0006,0.0003</t>
-  </si>
-  <si>
-    <t>0.0060,0.0008,0.9900,0.0038</t>
-  </si>
-  <si>
-    <t>0.0356,0.0226,0.9534,0.0069</t>
-  </si>
-  <si>
-    <t>0.6483,0.0024,0.3638,0.0290</t>
-  </si>
-  <si>
-    <t>0.0605,0.0077,0.9498,0.0016</t>
-  </si>
-  <si>
-    <t>0.0128,0.9843,0.0014,0.0001</t>
-  </si>
-  <si>
-    <t>0.0232,0.9783,0.0013,0.0006</t>
-  </si>
-  <si>
-    <t>0.0276,0.9700,0.0012,0.0009</t>
-  </si>
-  <si>
-    <t>0.2420,0.7673,0.0197,0.0036</t>
-  </si>
-  <si>
-    <t>0.0109,0.9788,0.0023,0.0008</t>
-  </si>
-  <si>
-    <t>0.0270,0.9531,0.0117,0.0014</t>
-  </si>
-  <si>
-    <t>0.4018,0.7012,0.0013,0.0032</t>
-  </si>
-  <si>
-    <t>0.8100,0.0467,0.1297,0.0194</t>
-  </si>
-  <si>
-    <t>0.5000,0.0078,0.6874,0.0044</t>
-  </si>
-  <si>
-    <t>0.1179,0.6318,0.0538,0.3975</t>
-  </si>
-  <si>
-    <t>0.6861,0.0272,0.3742,0.0020</t>
-  </si>
-  <si>
-    <t>0.3403,0.0853,0.0705,0.4847</t>
-  </si>
-  <si>
-    <t>0.0008,0.9958,0.0122,0.0003</t>
-  </si>
-  <si>
-    <t>0.0053,0.9772,0.0253,0.0022</t>
-  </si>
-  <si>
-    <t>0.1384,0.7674,0.1436,0.0798</t>
-  </si>
-  <si>
-    <t>0.0032,0.9054,0.8090,0.0019</t>
-  </si>
-  <si>
-    <t>0.0082,0.9790,0.1057,0.0002</t>
-  </si>
-  <si>
-    <t>0.5916,0.4549,0.0303,0.0020</t>
-  </si>
-  <si>
-    <t>0.6538,0.3522,0.0345,0.0006</t>
-  </si>
-  <si>
-    <t>0.9857,0.0063,0.0050,0.0007</t>
-  </si>
-  <si>
-    <t>0.9905,0.0041,0.0009,0.0009</t>
-  </si>
-  <si>
-    <t>0.9880,0.0055,0.0016,0.0019</t>
-  </si>
-  <si>
-    <t>0.9709,0.0221,0.0034,0.0022</t>
-  </si>
-  <si>
-    <t>0.9767,0.0031,0.0023,0.0109</t>
-  </si>
-  <si>
-    <t>0.9684,0.0232,0.0087,0.0014</t>
-  </si>
-  <si>
-    <t>0.9914,0.0019,0.0003,0.0026</t>
-  </si>
-  <si>
-    <t>0.9930,0.0009,0.0004,0.0022</t>
-  </si>
-  <si>
-    <t>0.0086,0.7146,0.8280,0.0025</t>
-  </si>
-  <si>
-    <t>0.0120,0.6237,0.8584,0.0016</t>
-  </si>
-  <si>
-    <t>0.0163,0.1649,0.9194,0.0058</t>
-  </si>
-  <si>
-    <t>0.0577,0.0854,0.8950,0.0011</t>
-  </si>
-  <si>
-    <t>0.9436,0.0212,0.0202,0.0012</t>
-  </si>
-  <si>
-    <t>0.7523,0.0235,0.3268,0.0028</t>
-  </si>
-  <si>
-    <t>0.3021,0.0106,0.8050,0.0164</t>
-  </si>
-  <si>
-    <t>0.2103,0.5935,0.1368,0.1872</t>
-  </si>
-  <si>
-    <t>0.0035,0.0019,0.0040,0.9948</t>
-  </si>
-  <si>
-    <t>0.0012,0.0001,0.0004,0.9987</t>
-  </si>
-  <si>
-    <t>0.0008,0.0293,0.0001,0.9990</t>
-  </si>
-  <si>
-    <t>0.0269,0.0015,0.0148,0.9756</t>
-  </si>
-  <si>
-    <t>0.0007,0.9837,0.2143,0.0006</t>
-  </si>
-  <si>
-    <t>0.9753,0.0087,0.0042,0.0051</t>
-  </si>
-  <si>
-    <t>0.0320,0.9588,0.0017,0.0063</t>
-  </si>
-  <si>
-    <t>0.9790,0.0004,0.0002,0.0256</t>
-  </si>
-  <si>
-    <t>0.4786,0.6914,0.0057,0.0019</t>
-  </si>
-  <si>
-    <t>0.9764,0.0112,0.0030,0.0042</t>
-  </si>
-  <si>
-    <t>0.3852,0.0120,0.0047,0.7618</t>
-  </si>
-  <si>
-    <t>0.9778,0.0031,0.0017,0.0102</t>
-  </si>
-  <si>
-    <t>0.0048,0.0364,0.9425,0.0887</t>
-  </si>
-  <si>
-    <t>0.6540,0.0111,0.0565,0.2878</t>
-  </si>
-  <si>
-    <t>0.9249,0.0040,0.0241,0.0298</t>
-  </si>
-  <si>
-    <t>0.2371,0.6838,0.1373,0.0151</t>
-  </si>
-  <si>
-    <t>0.8709,0.0845,0.0360,0.0033</t>
-  </si>
-  <si>
-    <t>0.9069,0.0444,0.0423,0.0012</t>
-  </si>
-  <si>
-    <t>0.1819,0.7251,0.1210,0.0137</t>
-  </si>
-  <si>
-    <t>0.8622,0.1317,0.0136,0.0008</t>
-  </si>
-  <si>
-    <t>0.8465,0.0909,0.0515,0.0072</t>
-  </si>
-  <si>
-    <t>0.9750,0.0104,0.0088,0.0029</t>
-  </si>
-  <si>
-    <t>0.9897,0.0038,0.0004,0.0019</t>
-  </si>
-  <si>
-    <t>0.9845,0.0028,0.0029,0.0035</t>
-  </si>
-  <si>
-    <t>0.9834,0.0033,0.0011,0.0058</t>
-  </si>
-  <si>
-    <t>0.9532,0.0259,0.0165,0.0031</t>
-  </si>
-  <si>
-    <t>0.9884,0.0060,0.0013,0.0011</t>
-  </si>
-  <si>
-    <t>0.9916,0.0025,0.0012,0.0012</t>
-  </si>
-  <si>
-    <t>0.9953,0.0009,0.0002,0.0011</t>
-  </si>
-  <si>
-    <t>0.6346,0.4620,0.0044,0.0026</t>
-  </si>
-  <si>
-    <t>0.4880,0.5890,0.0219,0.0027</t>
-  </si>
-  <si>
-    <t>0.7107,0.4063,0.0080,0.0013</t>
-  </si>
-  <si>
-    <t>0.0473,0.1639,0.9334,0.0014</t>
-  </si>
-  <si>
-    <t>0.9226,0.0725,0.0079,0.0034</t>
-  </si>
-  <si>
-    <t>0.9634,0.0119,0.0214,0.0029</t>
-  </si>
-  <si>
-    <t>0.9567,0.0623,0.0025,0.0005</t>
-  </si>
-  <si>
-    <t>0.8903,0.0786,0.0341,0.0012</t>
-  </si>
-  <si>
-    <t>0.0065,0.0185,0.9922,0.0012</t>
-  </si>
-  <si>
-    <t>0.9676,0.0188,0.0117,0.0016</t>
-  </si>
-  <si>
-    <t>0.0109,0.0026,0.9913,0.0003</t>
-  </si>
-  <si>
-    <t>0.0009,0.1870,0.9926,0.0006</t>
-  </si>
-  <si>
-    <t>0.0416,0.0101,0.9535,0.0040</t>
-  </si>
-  <si>
-    <t>0.0118,0.0304,0.9714,0.0043</t>
-  </si>
-  <si>
-    <t>0.0318,0.0456,0.9500,0.0002</t>
-  </si>
-  <si>
-    <t>0.0312,0.0054,0.9811,0.0001</t>
-  </si>
-  <si>
-    <t>0.0087,0.0472,0.9847,0.0004</t>
-  </si>
-  <si>
-    <t>0.2026,0.0463,0.7094,0.0292</t>
-  </si>
-  <si>
-    <t>0.1007,0.0483,0.8711,0.0015</t>
-  </si>
-  <si>
-    <t>0.2924,0.5044,0.1305,0.0248</t>
-  </si>
-  <si>
-    <t>0.3810,0.0822,0.6342,0.0063</t>
-  </si>
-  <si>
-    <t>0.2634,0.0940,0.7001,0.0077</t>
-  </si>
-  <si>
-    <t>0.1885,0.5441,0.2357,0.0092</t>
-  </si>
-  <si>
-    <t>0.4627,0.2368,0.3126,0.0113</t>
-  </si>
-  <si>
-    <t>0.4036,0.3849,0.2877,0.0392</t>
-  </si>
-  <si>
-    <t>0.6251,0.5092,0.0055,0.0023</t>
-  </si>
-  <si>
-    <t>0.4212,0.6718,0.0074,0.0018</t>
-  </si>
-  <si>
-    <t>0.7046,0.3364,0.0246,0.0013</t>
-  </si>
-  <si>
-    <t>0.9009,0.1668,0.0040,0.0004</t>
-  </si>
-  <si>
-    <t>0.5269,0.6614,0.0043,0.0015</t>
-  </si>
-  <si>
-    <t>0.7826,0.0097,0.2854,0.0140</t>
-  </si>
-  <si>
-    <t>0.8907,0.0205,0.0872,0.0049</t>
-  </si>
-  <si>
-    <t>0.6514,0.0284,0.3331,0.0221</t>
-  </si>
-  <si>
-    <t>0.8116,0.0188,0.2169,0.0018</t>
-  </si>
-  <si>
-    <t>0.8502,0.0270,0.1120,0.0108</t>
-  </si>
-  <si>
-    <t>0.0317,0.0337,0.8978,0.1073</t>
-  </si>
-  <si>
-    <t>0.0541,0.2775,0.7857,0.0050</t>
-  </si>
-  <si>
-    <t>0.0560,0.2196,0.8970,0.0163</t>
-  </si>
-  <si>
-    <t>0.0691,0.1452,0.8773,0.0026</t>
-  </si>
-  <si>
-    <t>0.0417,0.6077,0.3729,0.0485</t>
-  </si>
-  <si>
-    <t>0.9766,0.0109,0.0035,0.0033</t>
-  </si>
-  <si>
-    <t>0.9784,0.0195,0.0022,0.0011</t>
-  </si>
-  <si>
-    <t>0.9826,0.0205,0.0009,0.0005</t>
-  </si>
-  <si>
-    <t>0.9330,0.0662,0.0109,0.0011</t>
-  </si>
-  <si>
-    <t>0.9776,0.0215,0.0041,0.0006</t>
-  </si>
-  <si>
-    <t>0.9954,0.0017,0.0004,0.0004</t>
-  </si>
-  <si>
-    <t>0.9724,0.0150,0.0047,0.0023</t>
-  </si>
-  <si>
-    <t>0.9831,0.0173,0.0010,0.0007</t>
-  </si>
-  <si>
-    <t>0.1249,0.0124,0.9344,0.0023</t>
-  </si>
-  <si>
-    <t>0.4028,0.4449,0.2585,0.0434</t>
-  </si>
-  <si>
-    <t>0.8933,0.0114,0.1202,0.0037</t>
-  </si>
-  <si>
-    <t>0.0034,0.0432,0.9721,0.0121</t>
-  </si>
-  <si>
-    <t>0.0007,0.0074,0.9853,0.0225</t>
-  </si>
-  <si>
-    <t>0.0266,0.0138,0.9727,0.0005</t>
-  </si>
-  <si>
-    <t>0.0001,0.0007,0.9977,0.0061</t>
-  </si>
-  <si>
-    <t>0.0531,0.0240,0.9437,0.0023</t>
-  </si>
-  <si>
-    <t>0.0053,0.0323,0.9886,0.0025</t>
-  </si>
-  <si>
-    <t>0.2104,0.0236,0.8249,0.0024</t>
-  </si>
-  <si>
-    <t>0.2672,0.1166,0.6605,0.0251</t>
-  </si>
-  <si>
-    <t>0.8625,0.0029,0.2458,0.0027</t>
-  </si>
-  <si>
-    <t>0.8098,0.0041,0.2069,0.0132</t>
-  </si>
-  <si>
-    <t>0.9056,0.0041,0.1411,0.0007</t>
-  </si>
-  <si>
-    <t>0.9850,0.0101,0.0022,0.0007</t>
-  </si>
-  <si>
-    <t>0.9831,0.0177,0.0009,0.0005</t>
-  </si>
-  <si>
-    <t>0.9930,0.0022,0.0013,0.0005</t>
-  </si>
-  <si>
-    <t>0.9697,0.0283,0.0035,0.0013</t>
-  </si>
-  <si>
-    <t>0.9888,0.0036,0.0006,0.0026</t>
-  </si>
-  <si>
-    <t>0.9895,0.0081,0.0013,0.0003</t>
-  </si>
-  <si>
-    <t>0.9750,0.0217,0.0035,0.0009</t>
-  </si>
-  <si>
-    <t>0.9889,0.0063,0.0010,0.0010</t>
-  </si>
-  <si>
-    <t>0.0365,0.1985,0.8513,0.0109</t>
-  </si>
-  <si>
-    <t>0.0195,0.1574,0.9094,0.0137</t>
-  </si>
-  <si>
-    <t>0.0051,0.0109,0.9867,0.0034</t>
-  </si>
-  <si>
-    <t>0.1154,0.0824,0.8164,0.0065</t>
-  </si>
-  <si>
-    <t>0.0077,0.0200,0.9857,0.0017</t>
-  </si>
-  <si>
-    <t>0.3027,0.0132,0.3562,0.3749</t>
-  </si>
-  <si>
-    <t>0.2186,0.0612,0.6890,0.1058</t>
-  </si>
-  <si>
-    <t>0.0347,0.0455,0.8511,0.0974</t>
-  </si>
-  <si>
-    <t>0.5968,0.0007,0.0052,0.5759</t>
-  </si>
-  <si>
-    <t>0.0084,0.0205,0.0014,0.9942</t>
-  </si>
-  <si>
-    <t>0.0771,0.0208,0.0036,0.9682</t>
-  </si>
-  <si>
-    <t>0.0149,0.0013,0.0021,0.9916</t>
-  </si>
-  <si>
-    <t>0.0021,0.0002,0.0013,0.9978</t>
-  </si>
-  <si>
-    <t>0.7220,0.0499,0.0113,0.2349</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0.3934,0.2609,0.0410,0.5157</t>
+  </si>
+  <si>
+    <t>0.0024,0.0021,0.0014,0.9976</t>
+  </si>
+  <si>
+    <t>0.7562,0.0101,0.0174,0.2096</t>
+  </si>
+  <si>
+    <t>0.0205,0.0105,0.0005,0.9908</t>
+  </si>
+  <si>
+    <t>0.9983,0.0004,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9929,0.0060,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9921,0.0004,0.0002,0.0033</t>
+  </si>
+  <si>
+    <t>0.9969,0.0020,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9899,0.0051,0.0007,0.0010</t>
+  </si>
+  <si>
+    <t>0.9930,0.0033,0.0006,0.0004</t>
+  </si>
+  <si>
+    <t>0.9942,0.0021,0.0003,0.0006</t>
+  </si>
+  <si>
+    <t>0.9972,0.0009,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.5441,0.1271,0.4226,0.0374</t>
+  </si>
+  <si>
+    <t>0.1599,0.0645,0.8393,0.0032</t>
+  </si>
+  <si>
+    <t>0.1618,0.0917,0.8145,0.0014</t>
+  </si>
+  <si>
+    <t>0.1183,0.4272,0.5140,0.0115</t>
+  </si>
+  <si>
+    <t>0.7345,0.0787,0.2160,0.0078</t>
+  </si>
+  <si>
+    <t>0.0060,0.9807,0.0164,0.0047</t>
+  </si>
+  <si>
+    <t>0.0044,0.9917,0.0027,0.0001</t>
+  </si>
+  <si>
+    <t>0.1848,0.8375,0.0124,0.0014</t>
+  </si>
+  <si>
+    <t>0.0523,0.9520,0.0054,0.0013</t>
+  </si>
+  <si>
+    <t>0.0065,0.9855,0.0126,0.0002</t>
+  </si>
+  <si>
+    <t>0.7908,0.0080,0.1686,0.0201</t>
+  </si>
+  <si>
+    <t>0.3610,0.0604,0.5787,0.0666</t>
+  </si>
+  <si>
+    <t>0.0124,0.0095,0.9839,0.0004</t>
+  </si>
+  <si>
+    <t>0.1934,0.0097,0.8602,0.0032</t>
+  </si>
+  <si>
+    <t>0.0529,0.0121,0.9644,0.0007</t>
+  </si>
+  <si>
+    <t>0.1705,0.0032,0.9136,0.0021</t>
+  </si>
+  <si>
+    <t>0.0206,0.0038,0.9525,0.0508</t>
+  </si>
+  <si>
+    <t>0.3430,0.7150,0.0123,0.0007</t>
+  </si>
+  <si>
+    <t>0.1739,0.7458,0.1608,0.0224</t>
+  </si>
+  <si>
+    <t>0.0339,0.0345,0.9617,0.0095</t>
+  </si>
+  <si>
+    <t>0.0137,0.9493,0.1100,0.0028</t>
+  </si>
+  <si>
+    <t>0.8712,0.0684,0.0353,0.0087</t>
+  </si>
+  <si>
+    <t>0.7713,0.1899,0.0521,0.0136</t>
+  </si>
+  <si>
+    <t>0.4723,0.6105,0.0107,0.0023</t>
+  </si>
+  <si>
+    <t>0.0206,0.9355,0.1850,0.0008</t>
+  </si>
+  <si>
+    <t>0.0160,0.7018,0.3967,0.0244</t>
+  </si>
+  <si>
+    <t>0.2539,0.0344,0.8113,0.0083</t>
+  </si>
+  <si>
+    <t>0.0951,0.2138,0.7509,0.0024</t>
+  </si>
+  <si>
+    <t>0.1145,0.0167,0.7545,0.1491</t>
+  </si>
+  <si>
+    <t>0.0196,0.1331,0.9525,0.0041</t>
+  </si>
+  <si>
+    <t>0.0006,0.9910,0.0217,0.0021</t>
+  </si>
+  <si>
+    <t>0.0101,0.0492,0.9639,0.0114</t>
+  </si>
+  <si>
+    <t>0.0055,0.3486,0.0021,0.9893</t>
+  </si>
+  <si>
+    <t>0.0033,0.9884,0.0040,0.0013</t>
+  </si>
+  <si>
+    <t>0.0006,0.9945,0.0326,0.0002</t>
+  </si>
+  <si>
+    <t>0.0017,0.9922,0.0197,0.0006</t>
+  </si>
+  <si>
+    <t>0.0106,0.3068,0.9285,0.0046</t>
+  </si>
+  <si>
+    <t>0.0063,0.1422,0.9843,0.0002</t>
+  </si>
+  <si>
+    <t>0.1060,0.0070,0.9056,0.0143</t>
+  </si>
+  <si>
+    <t>0.0124,0.0033,0.9841,0.0048</t>
+  </si>
+  <si>
+    <t>0.0070,0.0067,0.9910,0.0012</t>
+  </si>
+  <si>
+    <t>0.0144,0.0969,0.9523,0.0008</t>
+  </si>
+  <si>
+    <t>0.9094,0.1294,0.0050,0.0007</t>
+  </si>
+  <si>
+    <t>0.9451,0.0237,0.0294,0.0039</t>
+  </si>
+  <si>
+    <t>0.9849,0.0072,0.0015,0.0024</t>
+  </si>
+  <si>
+    <t>0.0072,0.0256,0.9821,0.0121</t>
+  </si>
+  <si>
+    <t>0.9805,0.0089,0.0061,0.0019</t>
+  </si>
+  <si>
+    <t>0.9810,0.0146,0.0046,0.0008</t>
+  </si>
+  <si>
+    <t>0.9897,0.0056,0.0011,0.0011</t>
+  </si>
+  <si>
+    <t>0.0009,0.8170,0.9599,0.0001</t>
+  </si>
+  <si>
+    <t>0.0093,0.0402,0.9787,0.0016</t>
+  </si>
+  <si>
+    <t>0.0031,0.0393,0.9707,0.0176</t>
+  </si>
+  <si>
+    <t>0.0003,0.9151,0.9825,0.0000</t>
+  </si>
+  <si>
+    <t>0.0436,0.0245,0.9503,0.0037</t>
+  </si>
+  <si>
+    <t>0.0220,0.9327,0.0775,0.0019</t>
+  </si>
+  <si>
+    <t>0.0151,0.9851,0.0030,0.0000</t>
+  </si>
+  <si>
+    <t>0.9129,0.0133,0.0665,0.0152</t>
+  </si>
+  <si>
+    <t>0.2973,0.4707,0.3059,0.0084</t>
+  </si>
+  <si>
+    <t>0.0541,0.2053,0.8317,0.0006</t>
+  </si>
+  <si>
+    <t>0.0014,0.9291,0.8147,0.0001</t>
+  </si>
+  <si>
+    <t>0.0053,0.9072,0.5939,0.0007</t>
+  </si>
+  <si>
+    <t>0.0013,0.9856,0.1588,0.0002</t>
+  </si>
+  <si>
+    <t>0.0012,0.9366,0.8736,0.0001</t>
+  </si>
+  <si>
+    <t>0.0080,0.0374,0.0172,0.9838</t>
+  </si>
+  <si>
+    <t>0.0016,0.0120,0.0001,0.9987</t>
+  </si>
+  <si>
+    <t>0.0300,0.0009,0.0033,0.9829</t>
+  </si>
+  <si>
+    <t>0.0934,0.0031,0.0048,0.9636</t>
+  </si>
+  <si>
+    <t>0.0938,0.0077,0.0226,0.9316</t>
+  </si>
+  <si>
+    <t>0.0032,0.0050,0.0006,0.9974</t>
+  </si>
+  <si>
+    <t>0.0011,0.9591,0.5824,0.0006</t>
+  </si>
+  <si>
+    <t>0.0019,0.7784,0.9555,0.0001</t>
+  </si>
+  <si>
+    <t>0.0097,0.9315,0.1363,0.0152</t>
+  </si>
+  <si>
+    <t>0.0017,0.8980,0.8530,0.0004</t>
+  </si>
+  <si>
+    <t>0.0035,0.9380,0.6220,0.0002</t>
+  </si>
+  <si>
+    <t>0.0051,0.8673,0.8156,0.0013</t>
+  </si>
+  <si>
+    <t>0.9884,0.0064,0.0010,0.0009</t>
+  </si>
+  <si>
+    <t>0.9871,0.0147,0.0009,0.0003</t>
+  </si>
+  <si>
+    <t>0.9065,0.1319,0.0058,0.0005</t>
+  </si>
+  <si>
+    <t>0.9933,0.0039,0.0005,0.0003</t>
+  </si>
+  <si>
+    <t>0.9931,0.0012,0.0002,0.0019</t>
+  </si>
+  <si>
+    <t>0.9929,0.0045,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.9652,0.0245,0.0072,0.0025</t>
+  </si>
+  <si>
+    <t>0.9876,0.0073,0.0027,0.0007</t>
+  </si>
+  <si>
+    <t>0.9983,0.0004,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9907,0.0070,0.0013,0.0003</t>
+  </si>
+  <si>
+    <t>0.9983,0.0002,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.9891,0.0067,0.0018,0.0006</t>
+  </si>
+  <si>
+    <t>0.9838,0.0078,0.0022,0.0024</t>
+  </si>
+  <si>
+    <t>0.9956,0.0013,0.0001,0.0008</t>
+  </si>
+  <si>
+    <t>0.9953,0.0021,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9895,0.0047,0.0012,0.0010</t>
+  </si>
+  <si>
+    <t>0.0070,0.0050,0.9848,0.0085</t>
+  </si>
+  <si>
+    <t>0.0146,0.0373,0.9521,0.0215</t>
+  </si>
+  <si>
+    <t>0.4035,0.0086,0.6568,0.0209</t>
+  </si>
+  <si>
+    <t>0.2548,0.0151,0.8285,0.0052</t>
+  </si>
+  <si>
+    <t>0.0021,0.9941,0.0009,0.0011</t>
+  </si>
+  <si>
+    <t>0.0424,0.9568,0.0045,0.0005</t>
+  </si>
+  <si>
+    <t>0.0608,0.9508,0.0019,0.0015</t>
+  </si>
+  <si>
+    <t>0.1296,0.8764,0.0166,0.0016</t>
+  </si>
+  <si>
+    <t>0.0916,0.9066,0.0076,0.0027</t>
+  </si>
+  <si>
+    <t>0.0403,0.9680,0.0018,0.0003</t>
+  </si>
+  <si>
+    <t>0.1249,0.8644,0.0040,0.0079</t>
+  </si>
+  <si>
+    <t>0.6984,0.0677,0.2639,0.0119</t>
+  </si>
+  <si>
+    <t>0.4708,0.1297,0.4584,0.0265</t>
+  </si>
+  <si>
+    <t>0.6980,0.0472,0.2602,0.0122</t>
+  </si>
+  <si>
+    <t>0.4093,0.2027,0.2700,0.0057</t>
+  </si>
+  <si>
+    <t>0.0814,0.2177,0.0428,0.8975</t>
+  </si>
+  <si>
+    <t>0.0017,0.9903,0.0155,0.0012</t>
+  </si>
+  <si>
+    <t>0.0019,0.9854,0.0498,0.0030</t>
+  </si>
+  <si>
+    <t>0.0093,0.9300,0.0148,0.3425</t>
+  </si>
+  <si>
+    <t>0.0031,0.9702,0.4645,0.0003</t>
+  </si>
+  <si>
+    <t>0.0049,0.9869,0.0653,0.0001</t>
+  </si>
+  <si>
+    <t>0.4391,0.5273,0.0733,0.0040</t>
+  </si>
+  <si>
+    <t>0.7683,0.2277,0.0437,0.0010</t>
+  </si>
+  <si>
+    <t>0.9690,0.0246,0.0067,0.0013</t>
+  </si>
+  <si>
+    <t>0.9692,0.0150,0.0063,0.0044</t>
+  </si>
+  <si>
+    <t>0.9922,0.0009,0.0004,0.0019</t>
+  </si>
+  <si>
+    <t>0.9863,0.0038,0.0023,0.0028</t>
+  </si>
+  <si>
+    <t>0.9923,0.0035,0.0012,0.0005</t>
+  </si>
+  <si>
+    <t>0.9531,0.0304,0.0166,0.0034</t>
+  </si>
+  <si>
+    <t>0.9923,0.0015,0.0006,0.0023</t>
+  </si>
+  <si>
+    <t>0.9745,0.0158,0.0062,0.0016</t>
+  </si>
+  <si>
+    <t>0.0081,0.8040,0.7711,0.0033</t>
+  </si>
+  <si>
+    <t>0.0051,0.7703,0.8135,0.0008</t>
+  </si>
+  <si>
+    <t>0.0302,0.1732,0.9011,0.0051</t>
+  </si>
+  <si>
+    <t>0.0747,0.2176,0.7424,0.0010</t>
+  </si>
+  <si>
+    <t>0.8136,0.0940,0.0365,0.0400</t>
+  </si>
+  <si>
+    <t>0.7085,0.0883,0.2277,0.0065</t>
+  </si>
+  <si>
+    <t>0.2034,0.0109,0.8729,0.0071</t>
+  </si>
+  <si>
+    <t>0.5730,0.1555,0.2364,0.0024</t>
+  </si>
+  <si>
+    <t>0.0140,0.0041,0.0017,0.9926</t>
+  </si>
+  <si>
+    <t>0.0009,0.0002,0.0032,0.9976</t>
+  </si>
+  <si>
+    <t>0.0017,0.0051,0.0040,0.9959</t>
+  </si>
+  <si>
+    <t>0.0500,0.0022,0.0048,0.9774</t>
+  </si>
+  <si>
+    <t>0.0073,0.9003,0.6120,0.0021</t>
+  </si>
+  <si>
+    <t>0.9165,0.0914,0.0108,0.0026</t>
+  </si>
+  <si>
+    <t>0.6810,0.4276,0.0100,0.0059</t>
+  </si>
+  <si>
+    <t>0.9806,0.0028,0.0006,0.0095</t>
+  </si>
+  <si>
+    <t>0.5015,0.5875,0.0160,0.0047</t>
+  </si>
+  <si>
+    <t>0.9761,0.0018,0.0018,0.0111</t>
+  </si>
+  <si>
+    <t>0.8405,0.0076,0.0940,0.0386</t>
+  </si>
+  <si>
+    <t>0.9703,0.0197,0.0038,0.0024</t>
+  </si>
+  <si>
+    <t>0.0082,0.0450,0.9092,0.1210</t>
+  </si>
+  <si>
+    <t>0.8944,0.0025,0.0031,0.0837</t>
+  </si>
+  <si>
+    <t>0.9768,0.0024,0.0025,0.0082</t>
+  </si>
+  <si>
+    <t>0.5053,0.4735,0.0407,0.0158</t>
+  </si>
+  <si>
+    <t>0.8824,0.0593,0.0436,0.0021</t>
+  </si>
+  <si>
+    <t>0.8965,0.0432,0.0490,0.0067</t>
+  </si>
+  <si>
+    <t>0.0784,0.8166,0.1553,0.0188</t>
+  </si>
+  <si>
+    <t>0.6511,0.2797,0.0784,0.0058</t>
+  </si>
+  <si>
+    <t>0.9191,0.0397,0.0266,0.0041</t>
+  </si>
+  <si>
+    <t>0.9784,0.0098,0.0045,0.0026</t>
+  </si>
+  <si>
+    <t>0.9804,0.0138,0.0025,0.0020</t>
+  </si>
+  <si>
+    <t>0.9930,0.0017,0.0004,0.0013</t>
+  </si>
+  <si>
+    <t>0.9848,0.0059,0.0025,0.0017</t>
+  </si>
+  <si>
+    <t>0.9933,0.0019,0.0005,0.0012</t>
+  </si>
+  <si>
+    <t>0.9797,0.0111,0.0031,0.0034</t>
+  </si>
+  <si>
+    <t>0.9951,0.0005,0.0007,0.0011</t>
+  </si>
+  <si>
+    <t>0.9826,0.0106,0.0009,0.0020</t>
+  </si>
+  <si>
+    <t>0.2547,0.7241,0.0096,0.0090</t>
+  </si>
+  <si>
+    <t>0.5674,0.5458,0.0064,0.0019</t>
+  </si>
+  <si>
+    <t>0.6353,0.5023,0.0082,0.0016</t>
+  </si>
+  <si>
+    <t>0.4627,0.3389,0.3289,0.0117</t>
+  </si>
+  <si>
+    <t>0.9270,0.0823,0.0024,0.0038</t>
+  </si>
+  <si>
+    <t>0.9509,0.0228,0.0091,0.0049</t>
+  </si>
+  <si>
+    <t>0.9743,0.0265,0.0024,0.0012</t>
+  </si>
+  <si>
+    <t>0.9048,0.0896,0.0159,0.0023</t>
+  </si>
+  <si>
+    <t>0.0424,0.0560,0.9673,0.0021</t>
+  </si>
+  <si>
+    <t>0.9786,0.0119,0.0026,0.0026</t>
+  </si>
+  <si>
+    <t>0.0146,0.0089,0.9874,0.0005</t>
+  </si>
+  <si>
+    <t>0.0150,0.0630,0.9630,0.0052</t>
+  </si>
+  <si>
+    <t>0.0908,0.0053,0.9526,0.0022</t>
+  </si>
+  <si>
+    <t>0.1023,0.0405,0.8888,0.0009</t>
+  </si>
+  <si>
+    <t>0.0148,0.0154,0.9702,0.0042</t>
+  </si>
+  <si>
+    <t>0.0169,0.0031,0.9900,0.0005</t>
+  </si>
+  <si>
+    <t>0.0091,0.0617,0.9721,0.0007</t>
+  </si>
+  <si>
+    <t>0.3953,0.1978,0.5061,0.0366</t>
+  </si>
+  <si>
+    <t>0.7283,0.0416,0.2772,0.0031</t>
+  </si>
+  <si>
+    <t>0.3617,0.3555,0.3358,0.0187</t>
+  </si>
+  <si>
+    <t>0.1919,0.1362,0.7075,0.0015</t>
+  </si>
+  <si>
+    <t>0.1000,0.1975,0.7634,0.0009</t>
+  </si>
+  <si>
+    <t>0.8389,0.0661,0.0825,0.0023</t>
+  </si>
+  <si>
+    <t>0.5535,0.2174,0.2557,0.0315</t>
+  </si>
+  <si>
+    <t>0.2248,0.2203,0.6404,0.0055</t>
+  </si>
+  <si>
+    <t>0.3960,0.6574,0.0238,0.0029</t>
+  </si>
+  <si>
+    <t>0.2450,0.8041,0.0192,0.0013</t>
+  </si>
+  <si>
+    <t>0.6474,0.4684,0.0105,0.0019</t>
+  </si>
+  <si>
+    <t>0.9774,0.0212,0.0015,0.0011</t>
+  </si>
+  <si>
+    <t>0.7677,0.3638,0.0064,0.0016</t>
+  </si>
+  <si>
+    <t>0.5253,0.1897,0.3050,0.0666</t>
+  </si>
+  <si>
+    <t>0.7429,0.0790,0.2202,0.0096</t>
+  </si>
+  <si>
+    <t>0.8070,0.0383,0.1155,0.0234</t>
+  </si>
+  <si>
+    <t>0.7672,0.0134,0.2822,0.0169</t>
+  </si>
+  <si>
+    <t>0.8700,0.0182,0.1197,0.0067</t>
+  </si>
+  <si>
+    <t>0.0392,0.0369,0.9513,0.0091</t>
+  </si>
+  <si>
+    <t>0.1644,0.0757,0.7876,0.0505</t>
+  </si>
+  <si>
+    <t>0.1258,0.1162,0.7858,0.0739</t>
+  </si>
+  <si>
+    <t>0.1320,0.0290,0.9180,0.0037</t>
+  </si>
+  <si>
+    <t>0.0452,0.6070,0.6111,0.0194</t>
+  </si>
+  <si>
+    <t>0.9902,0.0029,0.0008,0.0016</t>
+  </si>
+  <si>
+    <t>0.9793,0.0152,0.0031,0.0014</t>
+  </si>
+  <si>
+    <t>0.9773,0.0150,0.0010,0.0018</t>
+  </si>
+  <si>
+    <t>0.9673,0.0310,0.0057,0.0015</t>
+  </si>
+  <si>
+    <t>0.9904,0.0052,0.0020,0.0005</t>
+  </si>
+  <si>
+    <t>0.9936,0.0047,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.9969,0.0005,0.0001,0.0007</t>
+  </si>
+  <si>
+    <t>0.9815,0.0101,0.0020,0.0023</t>
+  </si>
+  <si>
+    <t>0.0360,0.0208,0.9794,0.0004</t>
+  </si>
+  <si>
+    <t>0.3278,0.0645,0.7370,0.0060</t>
+  </si>
+  <si>
+    <t>0.9254,0.0073,0.0300,0.0198</t>
+  </si>
+  <si>
+    <t>0.0224,0.0254,0.9746,0.0016</t>
+  </si>
+  <si>
+    <t>0.0003,0.0026,0.9979,0.0022</t>
+  </si>
+  <si>
+    <t>0.1138,0.0293,0.8744,0.0012</t>
+  </si>
+  <si>
+    <t>0.0017,0.0019,0.9958,0.0018</t>
+  </si>
+  <si>
+    <t>0.0605,0.0959,0.8795,0.0100</t>
+  </si>
+  <si>
+    <t>0.0070,0.0203,0.9945,0.0003</t>
+  </si>
+  <si>
+    <t>0.0395,0.0261,0.9014,0.0357</t>
+  </si>
+  <si>
+    <t>0.0623,0.1040,0.8556,0.0135</t>
+  </si>
+  <si>
+    <t>0.8541,0.0028,0.2461,0.0025</t>
+  </si>
+  <si>
+    <t>0.7349,0.0022,0.4488,0.0058</t>
+  </si>
+  <si>
+    <t>0.8987,0.0069,0.1072,0.0030</t>
+  </si>
+  <si>
+    <t>0.9937,0.0042,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9893,0.0131,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.9951,0.0019,0.0005,0.0003</t>
+  </si>
+  <si>
+    <t>0.9405,0.0803,0.0046,0.0005</t>
+  </si>
+  <si>
+    <t>0.9785,0.0099,0.0014,0.0019</t>
+  </si>
+  <si>
+    <t>0.9903,0.0068,0.0014,0.0003</t>
+  </si>
+  <si>
+    <t>0.9898,0.0054,0.0014,0.0007</t>
+  </si>
+  <si>
+    <t>0.9494,0.0602,0.0054,0.0018</t>
+  </si>
+  <si>
+    <t>0.0773,0.0283,0.9130,0.0082</t>
+  </si>
+  <si>
+    <t>0.0012,0.1839,0.9915,0.0002</t>
+  </si>
+  <si>
+    <t>0.0259,0.0398,0.9585,0.0016</t>
+  </si>
+  <si>
+    <t>0.0981,0.0269,0.8834,0.0150</t>
+  </si>
+  <si>
+    <t>0.0165,0.0143,0.9675,0.0107</t>
+  </si>
+  <si>
+    <t>0.4764,0.0063,0.3430,0.1235</t>
+  </si>
+  <si>
+    <t>0.1489,0.0394,0.7084,0.1731</t>
+  </si>
+  <si>
+    <t>0.0045,0.0032,0.9408,0.1202</t>
+  </si>
+  <si>
+    <t>0.8901,0.0011,0.0119,0.0900</t>
+  </si>
+  <si>
+    <t>0.0196,0.0818,0.0068,0.9826</t>
+  </si>
+  <si>
+    <t>0.0179,0.0021,0.0008,0.9934</t>
+  </si>
+  <si>
+    <t>0.0074,0.0003,0.0021,0.9943</t>
+  </si>
+  <si>
+    <t>0.0074,0.0012,0.0102,0.9865</t>
+  </si>
+  <si>
+    <t>0.1741,0.0791,0.0595,0.8419</t>
   </si>
 </sst>
 </file>
@@ -1956,10 +1959,10 @@
         <v>259</v>
       </c>
       <c r="C2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1973,7 +1976,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1987,7 +1990,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2001,7 +2004,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2015,7 +2018,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2029,7 +2032,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2043,7 +2046,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2057,7 +2060,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2071,7 +2074,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2085,7 +2088,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2099,7 +2102,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2113,7 +2116,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2127,7 +2130,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2141,7 +2144,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2155,7 +2158,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2169,7 +2172,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2183,7 +2186,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2197,7 +2200,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2211,7 +2214,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2225,7 +2228,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2239,7 +2242,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2253,7 +2256,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2264,10 +2267,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2278,10 +2281,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2295,7 +2298,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2309,7 +2312,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2323,7 +2326,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2337,7 +2340,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2351,7 +2354,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2365,7 +2368,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2379,7 +2382,7 @@
         <v>262</v>
       </c>
       <c r="D32" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2393,7 +2396,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2407,7 +2410,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2421,7 +2424,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2435,7 +2438,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2446,10 +2449,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2463,7 +2466,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2474,10 +2477,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2491,7 +2494,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2502,10 +2505,10 @@
         <v>261</v>
       </c>
       <c r="C41" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2519,7 +2522,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2533,7 +2536,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2547,7 +2550,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2561,7 +2564,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2572,10 +2575,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="D46" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2589,7 +2592,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2603,7 +2606,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2617,7 +2620,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2631,7 +2634,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2645,7 +2648,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2659,7 +2662,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2673,7 +2676,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2687,7 +2690,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2701,7 +2704,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2715,7 +2718,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2729,7 +2732,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2743,7 +2746,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2757,7 +2760,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2771,7 +2774,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2785,7 +2788,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2799,7 +2802,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2813,7 +2816,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2827,7 +2830,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2841,7 +2844,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2855,7 +2858,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2869,7 +2872,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2883,7 +2886,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2897,7 +2900,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2911,7 +2914,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2922,10 +2925,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D71" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2939,7 +2942,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2953,7 +2956,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2964,10 +2967,10 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2981,7 +2984,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2995,7 +2998,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3009,7 +3012,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3023,7 +3026,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3037,7 +3040,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3051,7 +3054,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3065,7 +3068,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3079,7 +3082,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3093,7 +3096,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3107,7 +3110,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3118,10 +3121,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D85" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3135,7 +3138,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3149,7 +3152,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3163,7 +3166,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3177,7 +3180,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3191,7 +3194,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3205,7 +3208,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3219,7 +3222,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3233,7 +3236,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3247,7 +3250,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3261,7 +3264,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3275,7 +3278,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3289,7 +3292,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3303,7 +3306,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3317,7 +3320,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3331,7 +3334,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3345,7 +3348,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3359,7 +3362,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3373,7 +3376,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3387,7 +3390,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3401,7 +3404,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3415,7 +3418,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3426,10 +3429,10 @@
         <v>259</v>
       </c>
       <c r="C107" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D107" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3443,7 +3446,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3457,7 +3460,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3471,7 +3474,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3485,7 +3488,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3499,7 +3502,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3513,7 +3516,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3527,7 +3530,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3541,7 +3544,7 @@
         <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3555,7 +3558,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3566,10 +3569,10 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D117" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3580,10 +3583,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3594,10 +3597,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D119" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3608,10 +3611,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3625,7 +3628,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3639,7 +3642,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3653,7 +3656,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3664,10 +3667,10 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D124" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3681,7 +3684,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3692,10 +3695,10 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D126" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3709,7 +3712,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3723,7 +3726,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3737,7 +3740,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3751,7 +3754,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3765,7 +3768,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3779,7 +3782,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3793,7 +3796,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3807,7 +3810,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3821,7 +3824,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3835,7 +3838,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3849,7 +3852,7 @@
         <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3863,7 +3866,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3877,7 +3880,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3891,7 +3894,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3905,7 +3908,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3919,7 +3922,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3930,10 +3933,10 @@
         <v>259</v>
       </c>
       <c r="C143" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3947,7 +3950,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3961,7 +3964,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3975,7 +3978,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3989,7 +3992,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4000,10 +4003,10 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4017,7 +4020,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4028,10 +4031,10 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D150" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4045,7 +4048,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4056,10 +4059,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D152" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4073,7 +4076,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4084,10 +4087,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4101,7 +4104,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4115,7 +4118,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4129,7 +4132,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4143,7 +4146,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4154,10 +4157,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D159" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4171,7 +4174,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4185,7 +4188,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4199,7 +4202,7 @@
         <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4213,7 +4216,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4227,7 +4230,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4241,7 +4244,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4255,7 +4258,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4269,7 +4272,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4283,7 +4286,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4297,7 +4300,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4311,7 +4314,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4325,7 +4328,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4339,7 +4342,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4350,10 +4353,10 @@
         <v>259</v>
       </c>
       <c r="C173" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D173" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4364,10 +4367,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D174" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4378,10 +4381,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D175" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4392,10 +4395,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D176" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4409,7 +4412,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4423,7 +4426,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4437,7 +4440,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4451,7 +4454,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4465,7 +4468,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4479,7 +4482,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4493,7 +4496,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4507,7 +4510,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4521,7 +4524,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4535,7 +4538,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4549,7 +4552,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4563,7 +4566,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4577,7 +4580,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4591,7 +4594,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4602,10 +4605,10 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D191" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4616,10 +4619,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D192" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4633,7 +4636,7 @@
         <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4647,7 +4650,7 @@
         <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4658,10 +4661,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4675,7 +4678,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4686,10 +4689,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4703,7 +4706,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4717,7 +4720,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4731,7 +4734,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4745,7 +4748,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4756,10 +4759,10 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4773,7 +4776,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4787,7 +4790,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4801,7 +4804,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4815,7 +4818,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4829,7 +4832,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4843,7 +4846,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4857,7 +4860,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4871,7 +4874,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4885,7 +4888,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4896,10 +4899,10 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D212" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4913,7 +4916,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4927,7 +4930,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4941,7 +4944,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4955,7 +4958,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4969,7 +4972,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4983,7 +4986,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4997,7 +5000,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5011,7 +5014,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5025,7 +5028,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5036,10 +5039,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5053,7 +5056,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5067,7 +5070,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5081,7 +5084,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5095,7 +5098,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5109,7 +5112,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5123,7 +5126,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5137,7 +5140,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5151,7 +5154,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5165,7 +5168,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5179,7 +5182,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5193,7 +5196,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5207,7 +5210,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5221,7 +5224,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5235,7 +5238,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5249,7 +5252,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5263,7 +5266,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5277,7 +5280,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5291,7 +5294,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5305,7 +5308,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5319,7 +5322,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5333,7 +5336,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5347,7 +5350,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5361,7 +5364,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5375,7 +5378,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5389,7 +5392,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5400,10 +5403,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D248" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5417,7 +5420,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5431,7 +5434,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5442,10 +5445,10 @@
         <v>259</v>
       </c>
       <c r="C251" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5459,7 +5462,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5473,7 +5476,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5487,7 +5490,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5501,7 +5504,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5512,10 +5515,10 @@
         <v>259</v>
       </c>
       <c r="C256" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D256" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
   </sheetData>
